--- a/manuscript_v5/SI/S2_Table.xlsx
+++ b/manuscript_v5/SI/S2_Table.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S2 Table. Pairwise agreement and OS-threshold test characteristics: full cohort (A11), patients with RNA-seq data and the 12-month threshold (A2), against platinum status and the combined label, and at every threshold from 6 to 60 months (A13, exploratory).</t>
+          <t>S2 Table. Pairwise agreement and OS-threshold test characteristics: full cohort (A11), patients with RNA-seq data and the 12-month threshold (A2), against platinum status and the broad combined label, and at every threshold from 6 to 60 months (A13, exploratory).</t>
         </is>
       </c>
     </row>

--- a/manuscript_v5/SI/S2_Table.xlsx
+++ b/manuscript_v5/SI/S2_Table.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A2_os_sens_spec_rnaseq" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A9_os_label_metrics" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A13_threshold_sweep" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A19_ipcw" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +503,18 @@
         </is>
       </c>
       <c r="B6" t="inlineStr">
+        <is>
+          <t>A19: label_validity/outputs/a19_ipcw.csv (inverse-probability-of-censoring-weighted sensitivity, specificity and PPV at 18 and 24 months)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>source / note</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>A9 Part B/C: label_validity/outputs/a9_os_label_metrics.csv (κmax, PABAK)</t>
         </is>
@@ -5239,4 +5252,297 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>threshold_months</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ipcw_km</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ipcw_km_lo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ipcw_km_hi</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ipcw_cox</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n_unweighted</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_cox</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>censored_before_t</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>censored_before_t_with_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sensitivity</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2142857142857142</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2062553195722271</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1258230186202988</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2944666409095671</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1908059198531883</v>
+      </c>
+      <c r="H2" t="n">
+        <v>268</v>
+      </c>
+      <c r="I2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J2" t="n">
+        <v>69</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>specificity</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9782608695652174</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9787670749266382</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.956191569033734</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.994930101429445</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9768490419206082</v>
+      </c>
+      <c r="H3" t="n">
+        <v>268</v>
+      </c>
+      <c r="I3" t="n">
+        <v>245</v>
+      </c>
+      <c r="J3" t="n">
+        <v>69</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PPV</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8145410868413228</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.640981199892746</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9563434900205088</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8014002000758693</v>
+      </c>
+      <c r="H4" t="n">
+        <v>268</v>
+      </c>
+      <c r="I4" t="n">
+        <v>245</v>
+      </c>
+      <c r="J4" t="n">
+        <v>69</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sensitivity</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.3855421686746988</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3687703084435752</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2689092880649902</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4703686829146494</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3484450736053107</v>
+      </c>
+      <c r="H5" t="n">
+        <v>259</v>
+      </c>
+      <c r="I5" t="n">
+        <v>236</v>
+      </c>
+      <c r="J5" t="n">
+        <v>87</v>
+      </c>
+      <c r="K5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>specificity</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9400449342912032</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9044129390949144</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9724274848750224</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9447774199555442</v>
+      </c>
+      <c r="H6" t="n">
+        <v>259</v>
+      </c>
+      <c r="I6" t="n">
+        <v>236</v>
+      </c>
+      <c r="J6" t="n">
+        <v>87</v>
+      </c>
+      <c r="K6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PPV</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7389882566921832</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6038949446208721</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8723838627753168</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7608502032242034</v>
+      </c>
+      <c r="H7" t="n">
+        <v>259</v>
+      </c>
+      <c r="I7" t="n">
+        <v>236</v>
+      </c>
+      <c r="J7" t="n">
+        <v>87</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/manuscript_v5/SI/S2_Table.xlsx
+++ b/manuscript_v5/SI/S2_Table.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A9_os_label_metrics" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A13_threshold_sweep" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A19_ipcw" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A23_ipcw_variants" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -525,6 +526,286 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>threshold_months</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sensitivity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>specificity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ppv</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>max_weight</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ess</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>268</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2142857142857142</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9782608695652174</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>km_all489</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>268</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2062553195722271</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9787670749266382</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8145410868413228</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.171924984882124</v>
+      </c>
+      <c r="H3" t="n">
+        <v>267.9337430082971</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>km_status_known</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>268</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2109576487440675</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9786179363424592</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8177420829913249</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.031459069036454</v>
+      </c>
+      <c r="H4" t="n">
+        <v>267.9914425356196</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>km_stratified_by_status</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>268</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2113373921666078</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9786944958371876</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8203196553208512</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.039458455165692</v>
+      </c>
+      <c r="H5" t="n">
+        <v>267.9864477814791</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>unweighted</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>259</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3855421686746988</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>km_all489</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>259</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3687703084435752</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9400449342912032</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7389882566921832</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.234782292449544</v>
+      </c>
+      <c r="H7" t="n">
+        <v>258.7890278144102</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>km_status_known</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>259</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3747652294721948</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9395257089796468</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7421569298728592</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.073104612686982</v>
+      </c>
+      <c r="H8" t="n">
+        <v>258.9221980719457</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>km_stratified_by_status</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>259</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3789403577786688</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9398503064095112</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7435192890822637</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.076555805523622</v>
+      </c>
+      <c r="H9" t="n">
+        <v>258.9234515107105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
